--- a/results/reliability_eval/Llama-3-8B_toy-qa-dataset_sample_30_tokens_0.1_temp_factual_retrieval_scores_08-24-4.xlsx
+++ b/results/reliability_eval/Llama-3-8B_toy-qa-dataset_sample_30_tokens_0.1_temp_factual_retrieval_scores_08-24-4.xlsx
@@ -477,31 +477,31 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.5310422602089269</v>
+        <v>0.4758699254349627</v>
       </c>
       <c r="B2" t="n">
-        <v>0.7962421395353991</v>
+        <v>0.6537304655601406</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5310422602089269</v>
+        <v>0.4758699254349627</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7962421395353991</v>
+        <v>0.6537304655601406</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4843898385565053</v>
+        <v>0.5175020712510356</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7884511735304583</v>
+        <v>0.6572149342550453</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9938271604938271</v>
+        <v>0.9929577464788732</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9968181246857717</v>
+        <v>0.9953303152246814</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7428571428571429</v>
+        <v>0.6761904761904762</v>
       </c>
     </row>
   </sheetData>
